--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-26T15:37:29+00:00</t>
+    <t>2025-02-27T22:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T22:55:39+00:00</t>
+    <t>2025-03-02T19:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:26:20+00:00</t>
+    <t>2025-03-02T19:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-02T19:33:38+00:00</t>
+    <t>2025-03-03T11:01:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-03T11:01:42+00:00</t>
+    <t>2025-03-06T11:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:29:33+00:00</t>
+    <t>2025-03-06T11:49:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T11:49:07+00:00</t>
+    <t>2025-03-06T20:18:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/PSSDataAcquisitionForm</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/PSSDataAcquisitionForm</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:18:44+00:00</t>
+    <t>2025-03-06T20:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1028,7 +1028,7 @@
     <t>CodeValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/CodeValueSet}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/pss/StructureDefinition/CodeValueSet}
 </t>
   </si>
   <si>
@@ -1811,7 +1811,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="94.8515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="87.6953125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T20:59:35+00:00</t>
+    <t>2025-03-07T09:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T09:02:50+00:00</t>
+    <t>2025-03-07T12:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T12:27:18+00:00</t>
+    <t>2025-03-07T13:27:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:27:46+00:00</t>
+    <t>2025-03-11T13:06:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:06:04+00:00</t>
+    <t>2025-03-11T13:09:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T13:09:22+00:00</t>
+    <t>2025-03-24T11:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-24T11:01:18+00:00</t>
+    <t>2025-04-06T05:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
+++ b/branches/updated-examples/StructureDefinition-PSSDataAcquisitionForm.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-06T05:59:28+00:00</t>
+    <t>2025-04-06T06:02:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
